--- a/backend/results/weekly_calls_2026_W36.xlsx
+++ b/backend/results/weekly_calls_2026_W36.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,13 +570,246 @@
           <t>neutral</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>25</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>temp_1788185463384_sample_call_2.wav</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:23:19.333722Z</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>The call was focused on confirming required documents for a loan application.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>temp_1788524590494_sample_call_2.wav</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:24:29.571039Z</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>The call was between an agent named Pam from Windows and a customer inquiring about window-based marketing services. The agent explained their interactive display solution and attempted to schedule a demonstration with the company's VP. The customer seemed cooperative but mostly focused on setting up an appointment to understand the cost aspect.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Schedule demonstration with VP</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>temp_1788524646684_videoplayback (4) (1) - Copy.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04T16:18:27.978503Z</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>The call was a follow-up between an agent and a customer to discuss setting up a meeting to go over an online platform. No specific property requirements or real estate interests were identified.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>temp_1788538680637_videoplayback (25).m4a</t>
         </is>
       </c>
     </row>
